--- a/ig/DM-MARS-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="2455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="2527">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -597,12 +597,6 @@
     <t>Contrepulsion par ballon intraaortique (CPBIA)</t>
   </si>
   <si>
-    <t>0145</t>
-  </si>
-  <si>
-    <t>Coronarographie</t>
-  </si>
-  <si>
     <t>0146</t>
   </si>
   <si>
@@ -1773,12 +1767,6 @@
     <t>Thoracoscopie</t>
   </si>
   <si>
-    <t>0522</t>
-  </si>
-  <si>
-    <t>Prise en charge de la tuberculose</t>
-  </si>
-  <si>
     <t>0523</t>
   </si>
   <si>
@@ -3192,7 +3180,7 @@
     <t>0814</t>
   </si>
   <si>
-    <t>Soutien et écoute téléphonique</t>
+    <t xml:space="preserve">Soutien et écoute à distance (par téléphone et/ou par messagerie) </t>
   </si>
   <si>
     <t>0815</t>
@@ -5031,12 +5019,6 @@
     <t>Chirurgie percutanée du rein</t>
   </si>
   <si>
-    <t>1165</t>
-  </si>
-  <si>
-    <t>Chirurgie proctologique</t>
-  </si>
-  <si>
     <t>1167</t>
   </si>
   <si>
@@ -5829,18 +5811,6 @@
     <t>Échographie de datation de grossesse</t>
   </si>
   <si>
-    <t>1302</t>
-  </si>
-  <si>
-    <t>Echographie de mesure de la clarté nucale par PS agréé</t>
-  </si>
-  <si>
-    <t>1303</t>
-  </si>
-  <si>
-    <t>Échographie morphologique du 2ème trimestre</t>
-  </si>
-  <si>
     <t>1304</t>
   </si>
   <si>
@@ -6342,7 +6312,7 @@
     <t>1391</t>
   </si>
   <si>
-    <t>Maladies vectorielles à tique (Lyme…)</t>
+    <t>Prise en charge de maladies vectorielles à tique (Lyme…)</t>
   </si>
   <si>
     <t>1392</t>
@@ -6654,7 +6624,7 @@
     <t>1453</t>
   </si>
   <si>
-    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
+    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
   </si>
   <si>
     <t>1454</t>
@@ -7311,6 +7281,36 @@
     <t>Evaluation et suivi des addictions liées au chemsex (cathinones de synthèse, poppers, etc)</t>
   </si>
   <si>
+    <t>1565</t>
+  </si>
+  <si>
+    <t>Groupe « entendeurs de voix » - hallucinations auditives</t>
+  </si>
+  <si>
+    <t>1566</t>
+  </si>
+  <si>
+    <t>Groupe directives anticipées en psychiatrie</t>
+  </si>
+  <si>
+    <t>1567</t>
+  </si>
+  <si>
+    <t>Autodétermination par la participation des adhérents à la gestion de la structure</t>
+  </si>
+  <si>
+    <t>1568</t>
+  </si>
+  <si>
+    <t>Activités sociales, culturelles, sportives et de loisirs</t>
+  </si>
+  <si>
+    <t>1569</t>
+  </si>
+  <si>
+    <t>Dépôt de plainte sur site</t>
+  </si>
+  <si>
     <t>1570</t>
   </si>
   <si>
@@ -7369,6 +7369,222 @@
   </si>
   <si>
     <t>Centre de ressources et de compétences sclérose en plaques (SEP)</t>
+  </si>
+  <si>
+    <t>1580</t>
+  </si>
+  <si>
+    <t>Relayage courte durée (quelques heures par jour)</t>
+  </si>
+  <si>
+    <t>1581</t>
+  </si>
+  <si>
+    <t>Relayage longue durée (sur plusieurs jours)</t>
+  </si>
+  <si>
+    <t>1582</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en cardiologie</t>
+  </si>
+  <si>
+    <t>1583</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie cardiaque et gros vaisseaux</t>
+  </si>
+  <si>
+    <t>1584</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie digestive et viscérale</t>
+  </si>
+  <si>
+    <t>1585</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie maxillo-faciale et stomatologie</t>
+  </si>
+  <si>
+    <t>1586</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie orthopédique et traumatologie</t>
+  </si>
+  <si>
+    <t>1587</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique orthopédique et traumatologie</t>
+  </si>
+  <si>
+    <t>1588</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique viscérale et digestive</t>
+  </si>
+  <si>
+    <t>1589</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie thoracique et pulmonaire</t>
+  </si>
+  <si>
+    <t>1590</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie vasculaire</t>
+  </si>
+  <si>
+    <t>1591</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en dermatologie</t>
+  </si>
+  <si>
+    <t>1592</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en endocrinologie</t>
+  </si>
+  <si>
+    <t>1593</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gériatrie (gérontologie)</t>
+  </si>
+  <si>
+    <t>1594</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gynécologie</t>
+  </si>
+  <si>
+    <t>1595</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hématologie</t>
+  </si>
+  <si>
+    <t>1596</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hépato-gastro-entérologie</t>
+  </si>
+  <si>
+    <t>1597</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en maladies infectieuses et tropicales</t>
+  </si>
+  <si>
+    <t>1598</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine interne</t>
+  </si>
+  <si>
+    <t>1599</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine vasculaire</t>
+  </si>
+  <si>
+    <t>1600</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en néphrologie (dont dialyse)</t>
+  </si>
+  <si>
+    <t>1601</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurochirurgie</t>
+  </si>
+  <si>
+    <t>1602</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurologie</t>
+  </si>
+  <si>
+    <t>1603</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oncologie</t>
+  </si>
+  <si>
+    <t>1604</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en ophtalmologie</t>
+  </si>
+  <si>
+    <t>1605</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
+  </si>
+  <si>
+    <t>1606</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pédiatrie</t>
+  </si>
+  <si>
+    <t>1607</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pneumologie</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en rhumatologie</t>
+  </si>
+  <si>
+    <t>1609</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en urologie</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en caisson oxygène hyperbare</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie de la main SOS main</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en odontologie</t>
+  </si>
+  <si>
+    <t>1613</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en psychiatrie (dont équipe de liaison)</t>
+  </si>
+  <si>
+    <t>1614</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en radiologie interventionnelle</t>
+  </si>
+  <si>
+    <t>1615</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) rachis</t>
   </si>
   <si>
     <t/>
@@ -7639,7 +7855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1215"/>
+  <dimension ref="A1:B1251"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -17355,15 +17571,303 @@
         <v>2452</v>
       </c>
       <c r="B1214" t="s" s="2">
-        <v>2452</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="s" s="2">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="B1215" t="s" s="2">
-        <v>2454</v>
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="s" s="2">
+        <v>2456</v>
+      </c>
+      <c r="B1216" t="s" s="2">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="s" s="2">
+        <v>2458</v>
+      </c>
+      <c r="B1217" t="s" s="2">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="s" s="2">
+        <v>2460</v>
+      </c>
+      <c r="B1218" t="s" s="2">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="s" s="2">
+        <v>2462</v>
+      </c>
+      <c r="B1219" t="s" s="2">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="s" s="2">
+        <v>2464</v>
+      </c>
+      <c r="B1220" t="s" s="2">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="s" s="2">
+        <v>2466</v>
+      </c>
+      <c r="B1221" t="s" s="2">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="s" s="2">
+        <v>2468</v>
+      </c>
+      <c r="B1222" t="s" s="2">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="s" s="2">
+        <v>2470</v>
+      </c>
+      <c r="B1223" t="s" s="2">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="s" s="2">
+        <v>2472</v>
+      </c>
+      <c r="B1224" t="s" s="2">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="s" s="2">
+        <v>2474</v>
+      </c>
+      <c r="B1225" t="s" s="2">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="s" s="2">
+        <v>2476</v>
+      </c>
+      <c r="B1226" t="s" s="2">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="s" s="2">
+        <v>2478</v>
+      </c>
+      <c r="B1227" t="s" s="2">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="s" s="2">
+        <v>2480</v>
+      </c>
+      <c r="B1228" t="s" s="2">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="s" s="2">
+        <v>2482</v>
+      </c>
+      <c r="B1229" t="s" s="2">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="s" s="2">
+        <v>2484</v>
+      </c>
+      <c r="B1230" t="s" s="2">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="s" s="2">
+        <v>2486</v>
+      </c>
+      <c r="B1231" t="s" s="2">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="s" s="2">
+        <v>2488</v>
+      </c>
+      <c r="B1232" t="s" s="2">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="s" s="2">
+        <v>2490</v>
+      </c>
+      <c r="B1233" t="s" s="2">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="s" s="2">
+        <v>2492</v>
+      </c>
+      <c r="B1234" t="s" s="2">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="s" s="2">
+        <v>2494</v>
+      </c>
+      <c r="B1235" t="s" s="2">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="s" s="2">
+        <v>2496</v>
+      </c>
+      <c r="B1236" t="s" s="2">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="s" s="2">
+        <v>2498</v>
+      </c>
+      <c r="B1237" t="s" s="2">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="s" s="2">
+        <v>2500</v>
+      </c>
+      <c r="B1238" t="s" s="2">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="s" s="2">
+        <v>2502</v>
+      </c>
+      <c r="B1239" t="s" s="2">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="s" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B1240" t="s" s="2">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="s" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B1241" t="s" s="2">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="s" s="2">
+        <v>2508</v>
+      </c>
+      <c r="B1242" t="s" s="2">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="s" s="2">
+        <v>2510</v>
+      </c>
+      <c r="B1243" t="s" s="2">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="s" s="2">
+        <v>2512</v>
+      </c>
+      <c r="B1244" t="s" s="2">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="s" s="2">
+        <v>2514</v>
+      </c>
+      <c r="B1245" t="s" s="2">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="s" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B1246" t="s" s="2">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="s" s="2">
+        <v>2518</v>
+      </c>
+      <c r="B1247" t="s" s="2">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="s" s="2">
+        <v>2520</v>
+      </c>
+      <c r="B1248" t="s" s="2">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="s" s="2">
+        <v>2522</v>
+      </c>
+      <c r="B1249" t="s" s="2">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="s" s="2">
+        <v>2524</v>
+      </c>
+      <c r="B1250" t="s" s="2">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="s" s="2">
+        <v>2525</v>
+      </c>
+      <c r="B1251" t="s" s="2">
+        <v>2526</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-MARS-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -3180,7 +3180,7 @@
     <t>0814</t>
   </si>
   <si>
-    <t xml:space="preserve">Soutien et écoute à distance (par téléphone et/ou par messagerie) </t>
+    <t>Soutien et écoute à distance (par téléphone et/ou par messagerie)</t>
   </si>
   <si>
     <t>0815</t>
